--- a/research_DE.xlsx
+++ b/research_DE.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Free delivery within Germany ('Kostenloser Versand'; prices stated incl. delivery)</t>
+          <t>Free delivery ('Kostenloser Versand', prices 'inkl. Lieferung') from 30 EUR order value, mainland only; island surcharges extra</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>German pan-EU gastro supplier (GGM Gastro International, Ochtrup). On-screen prices load via JavaScript, but each product page's HTML carries schema.org price data for the de-de storefront (net and gross); those were recorded. Product URLs from GGM's public sitemap. B2B only. German prices are 2-15 EUR lower than on the Austrian storefront.</t>
+          <t>German pan-EU gastro supplier (GGM Gastro International, Ochtrup). On-screen prices load via JavaScript, but each product page's HTML carries schema.org price data for the de-de storefront (net and gross); those were recorded. Product URLs from GGM's public sitemap. B2B only. German prices are 2-15 EUR lower than on the Austrian storefront. Checked with a headless browser: the rendered on-screen price matches the recorded value (e.g. 44.99 net for the 6-pack GN 1/1 PC).</t>
         </is>
       </c>
     </row>
@@ -737,19 +737,19 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>SUBSTITUTE - added because LUSINI, Nisbets and METRO block access. German seller (Harotec GmbH), mostly Nisbets range (Vogue, Cambro, Hygiplas, Gastronoble) plus Bartscher. Same shop as gastroladen.at; DE gross prices are the AT gross prices recalculated at 19%.</t>
+          <t>SUBSTITUTE - added because LUSINI (incl. VEGA/PULSIVA) and METRO block access. German seller (Harotec GmbH), mostly Nisbets range (Vogue, Cambro, Hygiplas, Gastronoble) plus Bartscher. Same shop as gastroladen.at; DE gross prices are the AT gross prices recalculated at 19%.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de</t>
+          <t>https://www.nisbets.de</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>excl. VAT ('zzgl. 19% MwSt.')</t>
+          <t>excl. VAT by default ('Zzgl. MwSt.'; toggle to incl. VAT available)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Germany (and Austria): free from 99 EUR (incl. VAT) order value; below that 9.95 EUR (incl. VAT) flat; freight items by forwarder</t>
+          <t>Germany: free for orders over 100 EUR net; under 100 EUR net 9.95 EUR net (standard, 2-4 working days)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -778,26 +778,26 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>SUBSTITUTE - added because LUSINI, Nisbets and METRO block access. German gastro webshop (40,000+ items: Hendi, Contacto, WAS, APS, Rieber). Many Contacto items on 20% 'Sonderangebot' - sale price recorded, normal price in notes. Prices read on gastrodax.de on 2026-09-30.</t>
+          <t>Pan-EU gastro supplier (Nisbets; Vogue, Hygiplas, Cambro, Araven, Olympia ranges). Site is behind a Cloudflare check that blocks plain scripts; read with a headless Chromium browser (normal browsing, no bypass techniques). Many items show a reduced 'Web Preis' vs UVP; web price recorded. Some items have quantity tiers - single-unit (1+) price recorded.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com</t>
+          <t>https://www.gastrodax.de</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -807,33 +807,33 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2B + B2C</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>excl. VAT ('Preise zzgl. MwSt.'; gross shown at 19%)</t>
+          <t>excl. VAT ('zzgl. 19% MwSt.')</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Germany: standard 7.50 EUR (+7.50 express option, -7.50 'keine Eile' option); mainland only</t>
+          <t>Germany (and Austria): free from 99 EUR (incl. VAT) order value; below that 9.95 EUR (incl. VAT) flat; freight items by forwarder</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Minimum order value per warehouse 70 EUR net in Germany; below that a 25 EUR net small-quantity surcharge</t>
+          <t>none stated</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>SUBSTITUTE - added because LUSINI, Nisbets and METRO block access. German B2B webshop for business/gastro/hotel supplies (WAS and Schneider GN ranges). Current 'Verkaufspreis' recorded; regular price in notes. No squeeze bottles found.</t>
+          <t>SUBSTITUTE - added because LUSINI (incl. VEGA/PULSIVA) and METRO block access. German gastro webshop (40,000+ items: Hendi, Contacto, WAS, APS, Rieber). Many Contacto items on 20% 'Sonderangebot' - sale price recorded, normal price in notes. Prices read on gastrodax.de on 2026-09-30.</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1246,26 +1246,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>GN-Behälter - GN 1/1 (530 x 325 mm) - 65 mm - Inhalt 9,0 l - Polycarbonat</t>
+          <t>Vogue Polycarbonat GN-Behälter GN1/1 65mm</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/gn-behaelter-gn-1-1-530-x-325-mm-65-mm-inhalt-9-0-l-polycarbonat/530100-C</t>
+          <t>https://www.nisbets.de/vogue-polycarbonat-gn-behlter-65mm/u224</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>13.9</v>
+        <v>7.26</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>13.9</v>
+        <v>7.26</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Regular price 22.55</t>
+          <t>Reduced web price (UVP 15.29, -53%); 'Nicht vorrätig' (out of stock) on 2026-09-30</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1658,26 +1658,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>GN-Behälter - GN 1/2 (325 x 265 mm) - 150 mm - Inhalt 9,0 l - Polycarbonat</t>
+          <t>Vogue Polycarbonat GN-Behälter 1/2, 150mm, transparent</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/gn-behaelter-gn-1-2-325-x-265-mm-150-mm-inhalt-9-0-l-polycarbonat/530112-C</t>
+          <t>https://www.nisbets.de/vogue-polycarbonat-gn-behlter-150mm/u230</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>10.9</v>
+        <v>5.82</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>10.9</v>
+        <v>5.82</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Regular price 17.20</t>
+          <t>Reduced web price (UVP 12.19, -52%)</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2014,26 +2014,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GN-Behälter - Inhalt 3,8 l - GN 1/3 (325 x 176 mm) - 100 mm - Polypropylen</t>
+          <t>Cambro Polypropylen GN 1/3 Gastronorm-Behälter 100mm</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Cambro</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/gn-behaelter-inhalt-3-8-l-gn-1-3-325-x-176-mm-100-mm-polypropylen/530021-C</t>
+          <t>https://www.nisbets.de/cambro-polypropylen-gn-13-behlter-100mm/dw504</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.5</v>
+        <v>3.59</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>4.5</v>
+        <v>3.59</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Regular price 6.90</t>
+          <t>UVP 4.59; Nisbets Essentials HZ340 same spec 4.09</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2374,26 +2374,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>GN-Deckel - einrastend - GN 1/1 (530 x 325 mm) - Polypropylen</t>
+          <t>Nisbets Essentials Gastronorm-Deckel 1/1 aus Polypropylen, transparent</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Nisbets Essentials</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/gn-deckel-einrastend-gn-1-1-530-x-325-mm-polypropylen/530005-C</t>
+          <t>https://www.nisbets.de/nisbets-essentials-gastronorm-deckel-1zu1-aus-polypropylenkma-transparent/fa826</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="3" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Regular price 7.65. APS PP lid 82101-B: 4.20</t>
+          <t>UVP 6.49; Cambro soft-seal PP lid DM743: 6.09</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2793,35 +2793,35 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 1000 ml, PP, single tip</t>
+          <t>Squeeze bottle 500 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>(6 Stück) Quetschflasche mit mittlerer Membran - 946ml</t>
+          <t>Araven klare tropffreie Soßenflasche 50cl</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>Araven</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/6-stueck-quetschflasche-mit-mittlerer-membran-946ml-ffo-005</t>
+          <t>https://www.nisbets.de/araven-klare-tropffreie-soenflasche-50cl/cw112</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>31.99</v>
+        <v>2.69</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2829,15 +2829,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>set of 6</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>5.33</v>
+        <v>2.69</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -2846,7 +2842,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>946 ml, FIFO type; material not stated</t>
+          <t>500 ml, polyethylene (not PP), drip-free valve; Vogue 454 ml (E092) no longer listed</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2866,26 +2862,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>APS Quetschflasche, transparent, 1,025 L</t>
+          <t>(6 Stück) Quetschflasche mit mittlerer Membran - 946ml</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/aps-quetschflasche-transparent-1025-l-aps93259</t>
+          <t>https://www.ggmgastro.com/de-de-eur/6-stueck-quetschflasche-mit-mittlerer-membran-946ml-ffo-005</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1.95</v>
+        <v>31.99</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2893,11 +2889,15 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="n">
-        <v>1.95</v>
+        <v>5.33</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1025 ml, polyethylene (not PP); min. qty 2</t>
+          <t>946 ml, FIFO type; material not stated</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2926,26 +2926,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Contacto Quetschflasche 0,95 l</t>
+          <t>APS Quetschflasche, transparent, 1,025 L</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-quetschflasche-0-95-l</t>
+          <t>https://www.gastro-hero.de/products/aps-quetschflasche-transparent-1025-l-aps93259</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="3" t="n">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>950 ml, polyethylene, FIFO bottom-fill; sale price, normal 3.45</t>
+          <t>1025 ml, polyethylene (not PP); min. qty 2</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2986,30 +2986,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Vogue Quetschflasche klar 990ml</t>
+          <t>Contacto Quetschflasche 0,95 l</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Vogue</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/G16771B@GN-W832/Vogue-Quetschflasche-klar-990ml.htm</t>
+          <t>https://www.gastrodax.de/contacto-quetschflasche-0-95-l</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.79</v>
+        <v>2.76</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="3" t="n">
-        <v>3.18</v>
+        <v>2.76</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>990 ml, polyethylene (not PP)</t>
+          <t>950 ml, polyethylene, FIFO bottom-fill; sale price, normal 3.45</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3046,30 +3046,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Quetschflasche 1025 ml transparent Ø 80 mm H 265 mm</t>
+          <t>Vogue Quetschflasche klar 990ml</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/quetschflasche-1025-ml-transparent-80-mm-h-265-mm-985068</t>
+          <t>https://www.gastroladen.de/G16771B@GN-W832/Vogue-Quetschflasche-klar-990ml.htm</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.95</v>
+        <v>3.79</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>1.95</v>
+        <v>3.18</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1025 ml; material polyethylene (not PP)</t>
+          <t>990 ml, polyethylene (not PP)</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3097,35 +3097,35 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, triple tip</t>
+          <t>Squeeze bottle 1000 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Schneider Quetschflasche 950 ml, 3 Öffnungen</t>
+          <t>Quetschflasche 1025 ml transparent Ø 80 mm H 265 mm</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/schneider-quetschflasche-950-ml-3-oeffnungen-150621</t>
+          <t>https://www.intergastro.de/quetschflasche-1025-ml-transparent-80-mm-h-265-mm-985068</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3.89</v>
+        <v>1.95</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -3137,16 +3137,16 @@
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="3" t="n">
-        <v>3.89</v>
+        <v>1.95</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Triple tip PP but 950 ml instead of 500 ml; min. qty 8</t>
+          <t>1025 ml; material polyethylene (not PP)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3157,21 +3157,21 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, triple tip</t>
+          <t>Squeeze bottle 1000 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Vogue transparente Quetschflasche mit 3 Spritzdüsen 68cl</t>
+          <t>Vogue Quetschflasche für Saucen und Dressings transparent 994ml</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3181,15 +3181,15 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/G16771B@GN-CW725/Vogue-transparente-Quetschflasche-mit-3-Spritzd%C3%BCsen-68cl.htm</t>
+          <t>https://www.nisbets.de/vogue-quetschflasche-klar-990ml/w832</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3.89</v>
+        <v>1.79</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -3197,16 +3197,16 @@
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="3" t="n">
-        <v>3.27</v>
+        <v>1.79</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Triple tip but 680 ml instead of 500 ml; smallest triple-tip offered</t>
+          <t>994 ml, polyethylene (not PP); 1.49 each from 10 pcs</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Quetschflasche Kunststoff 950 ml 3 Öffnungen transparent</t>
+          <t>Schneider Quetschflasche 950 ml, 3 Öffnungen</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/quetschflasche-kunststoff-950-ml-3-oeffnungen-transparent-80-mm-h-291-mm-960754</t>
+          <t>https://www.gastro-hero.de/products/schneider-quetschflasche-950-ml-3-oeffnungen-150621</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>4.44</v>
+        <v>3.89</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>4.44</v>
+        <v>3.89</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Triple tip PP bottle but 950 ml instead of 500 ml; no 500 ml triple-tip found</t>
+          <t>Triple tip PP but 950 ml instead of 500 ml; min. qty 8</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3277,35 +3277,39 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 500 ml, triple tip</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Saucenspender (für Senf, Ketchup, Mayonnaise), 2 l</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Vogue transparente Quetschflasche mit 3 Spritzdüsen 68cl</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.de/product_info.php/info/p12858_Saucenspender.html</t>
+          <t>https://www.gastroladen.de/G16771B@GN-CW725/Vogue-transparente-Quetschflasche-mit-3-Spritzd%C3%BCsen-68cl.htm</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>36.1</v>
+        <v>3.89</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -3313,16 +3317,16 @@
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>36.1</v>
+        <v>3.27</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Sauce pump dispenser 2 l (17x14x15.5 cm); price shown for default 2 l size; stand not mentioned</t>
+          <t>Triple tip but 680 ml instead of 500 ml; smallest triple-tip offered</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3333,35 +3337,35 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 500 ml, triple tip</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Ketchup / Saucenspender - 2 Liter - Polypropylen - mit Pumpe</t>
+          <t>Quetschflasche Kunststoff 950 ml 3 Öffnungen transparent</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/ketchup-saucenspender-2-liter-polypropylen-mit-pumpe-ksp2</t>
+          <t>https://www.intergastro.de/quetschflasche-kunststoff-950-ml-3-oeffnungen-transparent-80-mm-h-291-mm-960754</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>24.99</v>
+        <v>4.44</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3373,16 +3377,16 @@
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="3" t="n">
-        <v>24.99</v>
+        <v>4.44</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>210x220x210 mm, PP with pump</t>
+          <t>Triple tip PP bottle but 950 ml instead of 500 ml; no 500 ml triple-tip found</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3393,35 +3397,35 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 500 ml, triple tip</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Hendi Pump-Saucenspender, 2,5L, Weiß</t>
+          <t>Vogue klare Quetschflasche mit 3 Düsen 681ml</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/hendi-pump-saucenspender-2-5l-wei-c3-9f-230x210x-h-250mm</t>
+          <t>https://www.nisbets.de/vogue-klare-quetschflasche-mit-3-dsen-24oz/cw725</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>18.09</v>
+        <v>2.29</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3433,16 +3437,16 @@
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="3" t="n">
-        <v>18.09</v>
+        <v>2.29</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>ABS housing/stand with pump</t>
+          <t>Triple tip but 681 ml instead of 500 ml</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3462,26 +3466,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>ALLPAX</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Hendi Pump-Saucenspender, 2,5L, Weiß, 230x210x(H)327mm</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Hendi</t>
-        </is>
-      </c>
+          <t>Saucenspender (für Senf, Ketchup, Mayonnaise), 2 l</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-pump-sossenspender-weiss</t>
+          <t>https://www.allpax.de/product_info.php/info/p12858_Saucenspender.html</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>19.76</v>
+        <v>36.1</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3493,16 +3493,16 @@
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="3" t="n">
-        <v>19.76</v>
+        <v>36.1</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>ABS housing/stand with PP sauce container, lid and pump</t>
+          <t>Sauce pump dispenser 2 l (17x14x15.5 cm); price shown for default 2 l size; stand not mentioned</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3522,30 +3522,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Araven Soßenspender GN 1/9 Transparent 1,5L</t>
+          <t>Ketchup / Saucenspender - 2 Liter - Polypropylen - mit Pumpe</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Araven</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/3300@GN-CR821/Araven-So%C3%9Fenspender-GN-1-9-Transparent-1-5L.htm</t>
+          <t>https://www.ggmgastro.com/de-de-eur/ketchup-saucenspender-2-liter-polypropylen-mit-pumpe-ksp2</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>35.9</v>
+        <v>24.99</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -3553,16 +3553,16 @@
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="3" t="n">
-        <v>30.17</v>
+        <v>24.99</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>PP pump dispenser 1.5 l; stand only included in 2-/3-piece sets (3-set with acrylic stand also offered)</t>
+          <t>210x220x210 mm, PP with pump</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3582,26 +3582,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Druckknopf-Dosierspender rot 2 ltr Ø 98 mm H 440 mm</t>
+          <t>Hendi Pump-Saucenspender, 2,5L, Weiß</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/druckknopf-dosierspender-rot-2-ltr-98-mm-h-440-mm-100247</t>
+          <t>https://www.gastro-hero.de/products/hendi-pump-saucenspender-2-5l-wei-c3-9f-230x210x-h-250mm</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>93.66</v>
+        <v>18.09</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3613,16 +3613,16 @@
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="3" t="n">
-        <v>93.66</v>
+        <v>18.09</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Free-standing glass/stainless push-button sauce pump dispenser, 2 l</t>
+          <t>ABS housing/stand with pump</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3642,26 +3642,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Dosierspender - mit Druckknopf - 18,0 x 14,5 x 29,0 cm - Inhalt 2,0 l - Polyethylen</t>
+          <t>Hendi Pump-Saucenspender, 2,5L, Weiß, 230x210x(H)327mm</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/dosierspender-mit-druckknopf-18-0-x-14-5-x-29-0-cm-inhalt-2-0-l-polyethylen/154710-C</t>
+          <t>https://www.gastrodax.de/hendi-pump-sossenspender-weiss</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>30.5</v>
+        <v>19.76</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -3673,16 +3673,16 @@
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="3" t="n">
-        <v>30.5</v>
+        <v>19.76</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Push-button sauce pump dispenser 2 l, free-standing; regular price 49.20</t>
+          <t>ABS housing/stand with PP sauce container, lid and pump</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3693,39 +3693,39 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett PRO 53x32 W-R</t>
+          <t>Araven Soßenspender GN 1/9 Transparent 1,5L</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Bartscher</t>
+          <t>Araven</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.de/product_info.php/info/Schneidbrett-PRO-53x32-W-R.html</t>
+          <t>https://www.gastroladen.de/3300@GN-CR821/Araven-So%C3%9Fenspender-GN-1-9-Transparent-1-5L.htm</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>26.95</v>
+        <v>35.9</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -3733,16 +3733,16 @@
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="3" t="n">
-        <v>26.95</v>
+        <v>30.17</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>HDPE white, 20 mm plate, juice groove, 530x325x24 mm incl. feet</t>
+          <t>PP pump dispenser 1.5 l; stand only included in 2-/3-piece sets (3-set with acrylic stand also offered)</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3753,35 +3753,35 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Schneidebrett - 325x530mm - HACCP-Konform - Weiß</t>
+          <t>Druckknopf-Dosierspender rot 2 ltr Ø 98 mm H 440 mm</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/schneidebrett-325x530mm-haccp-konform-weiss-sbp53w</t>
+          <t>https://www.intergastro.de/druckknopf-dosierspender-rot-2-ltr-98-mm-h-440-mm-100247</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>23.49</v>
+        <v>93.66</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -3793,16 +3793,16 @@
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="3" t="n">
-        <v>23.49</v>
+        <v>93.66</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>PE, 325x530x20 mm</t>
+          <t>Free-standing glass/stainless push-button sauce pump dispenser, 2 l</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3813,35 +3813,35 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett GN 1/1 - 53 x 32,5 x 1,5 cm - HDPE blau</t>
+          <t>Araven Soßenspender GN 1/9 Transparent 1,5Ltr</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Araven</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/schneidbrett-gn-1-1-53-x-32-5-x-1-5-cm-hdpe-blau</t>
+          <t>https://www.nisbets.de/araven-soenspender-gn-19-transparent-15l/cr821</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>17.29</v>
+        <v>27.49</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="3" t="n">
-        <v>17.29</v>
+        <v>27.49</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>15 mm instead of 20 mm</t>
+          <t>PP pump dispenser 1.5 l, no stand; 3-piece set with stand (CR823) 111.99</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3882,26 +3882,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>ALLPAX</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Hendi Schneidbrett HACCP Gastronorm 1/1, Weiß, 530x325mm</t>
+          <t>Schneidbrett PRO 53x32 W-R</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Bartscher</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-gastronorm-1-1-gn-1-1-weiss-530-x-325-mm</t>
+          <t>https://www.allpax.de/product_info.php/info/Schneidbrett-PRO-53x32-W-R.html</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>20.95</v>
+        <v>26.95</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3913,16 +3913,16 @@
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="3" t="n">
-        <v>20.95</v>
+        <v>26.95</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>15 mm thick instead of 20 mm; all HACCP colours same price</t>
+          <t>HDPE white, 20 mm plate, juice groove, 530x325x24 mm incl. feet</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3942,30 +3942,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Bartscher Schneidbrett PRO 53x32 W-R</t>
+          <t>Schneidebrett - 325x530mm - HACCP-Konform - Weiß</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Bartscher</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/2310@A120511/Bartscher-Schneidbrett-PRO-53x32-W-R.htm</t>
+          <t>https://www.ggmgastro.com/de-de-eur/schneidebrett-325x530mm-haccp-konform-weiss-sbp53w</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>29.29</v>
+        <v>23.49</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="3" t="n">
-        <v>24.61</v>
+        <v>23.49</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>PE, 20 mm plate, HACCP white, rubber feet (530x24x325 overall)</t>
+          <t>PE, 325x530x20 mm</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4002,26 +4002,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>HACCP Schneidbrett Polyethylen weiß 530 x 325 mm H 20 mm</t>
+          <t>Schneidbrett GN 1/1 - 53 x 32,5 x 1,5 cm - HDPE blau</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/haccp-schneidbrett-polyethylen-weiss-530-mm-x-325-mm-h-20-mm-159115</t>
+          <t>https://www.gastro-hero.de/products/schneidbrett-gn-1-1-53-x-32-5-x-1-5-cm-hdpe-blau</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>22.09</v>
+        <v>17.29</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -4033,16 +4033,16 @@
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="3" t="n">
-        <v>22.09</v>
+        <v>17.29</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>White; other HACCP colours listed separately</t>
+          <t>15 mm instead of 20 mm</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4062,26 +4062,26 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>HACCP Schneidbrett - GN 1/1 - weiß - 2,0 cm - Polyethylen</t>
+          <t>Hendi Schneidbrett HACCP Gastronorm 1/1, Weiß, 530x325mm</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/haccp-schneidbrett-gn-1-1-weiss-2-0-cm-polyethylen/1830530-A</t>
+          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-gastronorm-1-1-gn-1-1-weiss-530-x-325-mm</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>18</v>
+        <v>20.95</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -4093,16 +4093,16 @@
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="3" t="n">
-        <v>18</v>
+        <v>20.95</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Regular price 27.00</t>
+          <t>15 mm thick instead of 20 mm; all HACCP colours same price</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4113,35 +4113,39 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett farbig 600 x 400 x 20 mm</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>Bartscher Schneidbrett PRO 53x32 W-R</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Bartscher</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.de/product_info.php/info/p30393_Schneidbrett-farbig-600-x-400-x-20-mm.html</t>
+          <t>https://www.gastroladen.de/2310@A120511/Bartscher-Schneidbrett-PRO-53x32-W-R.htm</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>49.39</v>
+        <v>29.29</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
@@ -4149,16 +4153,16 @@
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="3" t="n">
-        <v>49.39</v>
+        <v>24.61</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>600x400x20 mm, 5 colours, rubber feet; material not stated. Bartscher 60x40 white (16 mm) 34.61</t>
+          <t>PE, 20 mm plate, HACCP white, rubber feet (530x24x325 overall)</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4169,35 +4173,35 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Schneidebrett - EN 600x400 - HACCP-Konform - Weiß</t>
+          <t>HACCP Schneidbrett Polyethylen weiß 530 x 325 mm H 20 mm</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/schneidebrett-en-600x400-haccp-konform-weiss-sbp46w</t>
+          <t>https://www.intergastro.de/haccp-schneidbrett-polyethylen-weiss-530-mm-x-325-mm-h-20-mm-159115</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>28.49</v>
+        <v>22.09</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -4209,7 +4213,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="3" t="n">
-        <v>28.49</v>
+        <v>22.09</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
@@ -4218,7 +4222,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>PE, 600x400x20 mm</t>
+          <t>White; other HACCP colours listed separately</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4229,35 +4233,35 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Schneidebrett Gastro-M 600x400 weiß</t>
+          <t>Gastro M Schneidebrett GN1/1 braun</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Gastro-M</t>
+          <t>Gastro M</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/schneidebrett-gastro-m-600x400-weiss-gn344</t>
+          <t>https://www.nisbets.de/gastro-m-schneidebrett-braun/gn340</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>45.9</v>
+        <v>31.04</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -4269,7 +4273,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="3" t="n">
-        <v>45.9</v>
+        <v>31.04</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
@@ -4278,7 +4282,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>600x400x20 mm; material not stated on page</t>
+          <t>HDPE 530x325 but 15 mm thick (not 20); out of stock; UVP 37.49</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4298,26 +4302,22 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>ALLPAX</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Hendi Schneidbretter HACCP 600x400, Weiß</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Hendi</t>
-        </is>
-      </c>
+          <t>Schneidbrett farbig 600 x 400 x 20 mm</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-600-x-400-mm-weiss</t>
+          <t>https://www.allpax.de/product_info.php/info/p30393_Schneidbrett-farbig-600-x-400-x-20-mm.html</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>33.5</v>
+        <v>49.39</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="3" t="n">
-        <v>33.5</v>
+        <v>49.39</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>18 mm thick instead of 20 mm</t>
+          <t>600x400x20 mm, 5 colours, rubber feet; material not stated. Bartscher 60x40 white (16 mm) 34.61</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4358,30 +4358,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Bartscher Schneidbrett 60x40 W</t>
+          <t>Schneidebrett - EN 600x400 - HACCP-Konform - Weiß</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Bartscher</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/2310@A120592/Bartscher-Schneidbrett-60x40-W.htm</t>
+          <t>https://www.ggmgastro.com/de-de-eur/schneidebrett-en-600x400-haccp-konform-weiss-sbp46w</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>34.9</v>
+        <v>28.49</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
@@ -4389,16 +4389,16 @@
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="3" t="n">
-        <v>29.33</v>
+        <v>28.49</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>PE, 16 mm plate (20 mm incl. feet), HACCP white</t>
+          <t>PE, 600x400x20 mm</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4418,26 +4418,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett Polyethylen weiß mit Saftrille 600 x 400 mm</t>
+          <t>Schneidebrett Gastro-M 600x400 weiß</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Gastro-M</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/schneidbrett-polyethylen-weiss-mit-saftrille-600-mm-x-400-mm-159019</t>
+          <t>https://www.gastro-hero.de/products/schneidebrett-gastro-m-600x400-weiss-gn344</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>35.05</v>
+        <v>45.9</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -4449,16 +4449,16 @@
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="3" t="n">
-        <v>35.05</v>
+        <v>45.9</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>20 mm thick, with juice groove</t>
+          <t>600x400x20 mm; material not stated on page</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4469,35 +4469,35 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Schneidebrett - 250x400mm - HACCP-Konform - Weiß</t>
+          <t>Hendi Schneidbretter HACCP 600x400, Weiß</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/schneidebrett-250x400mm-haccp-konform-weiss-sbp25w</t>
+          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-600-x-400-mm-weiss</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>15.99</v>
+        <v>33.5</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -4509,16 +4509,16 @@
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="3" t="n">
-        <v>15.99</v>
+        <v>33.5</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Smallest HACCP board offered: 250x400 mm (vs 300x200x10); thickness not stated</t>
+          <t>18 mm thick instead of 20 mm</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4529,39 +4529,39 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett GN 1/2 - 32,5 x 26,5 x 1,2 cm - HDPE weiß</t>
+          <t>Bartscher Schneidbrett 60x40 W</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Bartscher</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/schneidbrett-gn-1-2-32-5-x-26-5-x-1-2-cm-hdpe-weiss</t>
+          <t>https://www.gastroladen.de/2310@A120592/Bartscher-Schneidbrett-60x40-W.htm</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>8.09</v>
+        <v>34.9</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
@@ -4569,16 +4569,16 @@
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="3" t="n">
-        <v>8.09</v>
+        <v>29.33</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>325x265x12 mm (GN 1/2) vs 300x200x10; no 300x200 board found</t>
+          <t>PE, 16 mm plate (20 mm incl. feet), HACCP white</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -4589,35 +4589,35 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Hendi Schneidbrett mit Griff, Weiß, 300x200mm</t>
+          <t>Schneidbrett Polyethylen weiß mit Saftrille 600 x 400 mm</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-schneidbrett-mit-griff-weiss-300-x-200-mm</t>
+          <t>https://www.intergastro.de/schneidbrett-polyethylen-weiss-mit-saftrille-600-mm-x-400-mm-159019</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>15.76</v>
+        <v>35.05</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="3" t="n">
-        <v>15.76</v>
+        <v>35.05</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>300x200x10 mm HDPE, with handle</t>
+          <t>20 mm thick, with juice groove</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -4649,39 +4649,39 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Hygiplas HDPE kleines Schneidebrett weiß 300x225x12mm</t>
+          <t>Gastro M HDPE Schneidebrett blau 60x40x2cm</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Hygiplas</t>
+          <t>Gastro M</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/2310@GN-HC867/Hygiplas-HDPE-kleines-Schneidebrett-wei%C3%9F-300x-225x12mm.htm</t>
+          <t>https://www.nisbets.de/gastro-m-hdpe-schneidebrett-blau/gn348</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>57.99</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -4689,16 +4689,16 @@
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="3" t="n">
-        <v>7.39</v>
+        <v>57.99</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>300x225x12 mm vs 300x200x10</t>
+          <t>HDPE 600x400x20 mm. Hygiplas 600x450x12 mm HDPE (J017 etc.) 25.49</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -4718,26 +4718,26 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett Polyethylen weiß 300 x 200 mm H 15 mm</t>
+          <t>Schneidebrett - 250x400mm - HACCP-Konform - Weiß</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/schneidbrett-polyethylen-weiss-300-mm-x-200-mm-h-15-mm-158986</t>
+          <t>https://www.ggmgastro.com/de-de-eur/schneidebrett-250x400mm-haccp-konform-weiss-sbp25w</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>8.74</v>
+        <v>15.99</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -4749,16 +4749,16 @@
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="3" t="n">
-        <v>8.74</v>
+        <v>15.99</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>15 mm thick instead of 10 mm</t>
+          <t>Smallest HACCP board offered: 250x400 mm (vs 300x200x10); thickness not stated</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -4769,35 +4769,35 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>AmerBox Pizzaballenbox 60 x 40 x 9,5 cm</t>
+          <t>Schneidbrett GN 1/2 - 32,5 x 26,5 x 1,2 cm - HDPE weiß</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>AmerBox</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.de/product_info.php/info/AmerBox-Pizzaballenbox-60-x-40-x-9-5-cm.html</t>
+          <t>https://www.gastro-hero.de/products/schneidbrett-gn-1-2-32-5-x-26-5-x-1-2-cm-hdpe-weiss</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>13.95</v>
+        <v>8.09</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -4809,16 +4809,16 @@
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="3" t="n">
-        <v>13.95</v>
+        <v>8.09</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>95 mm high and polyethylene (vs 100 mm PP), 18 l</t>
+          <t>325x265x12 mm (GN 1/2) vs 300x200x10; no 300x200 board found</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -4829,35 +4829,35 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>9-tlg Teigbehälter-Set - 8 Behälter &amp; 1 Deckel - EN 600x400 - Höhe: 100mm - Polypropylen</t>
+          <t>Hendi Schneidbrett mit Griff, Weiß, 300x200mm</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/9-tlg-teigbehaelter-set-8-behaelter-und-1-deckel-en-600x400-hoehe-100mm-polypropylen-weiss-tbpp6410</t>
+          <t>https://www.gastrodax.de/hendi-schneidbrett-mit-griff-weiss-300-x-200-mm</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>73.98999999999999</v>
+        <v>15.76</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -4865,24 +4865,20 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>8 boxes + 1 lid</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="3" t="n">
-        <v>9.25</v>
+        <v>15.76</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Only sold as a set of 8 boxes plus 1 lid; net per box includes a share of the lid</t>
+          <t>300x200x10 mm HDPE, with handle</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -4893,39 +4889,39 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Pizzateigbox 18 l 600x400x95 mm</t>
+          <t>Hygiplas HDPE kleines Schneidebrett weiß 300x225x12mm</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Hygiplas</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/pizzateigbox-18-l-600x400x95-mm</t>
+          <t>https://www.gastroladen.de/2310@GN-HC867/Hygiplas-HDPE-kleines-Schneidebrett-wei%C3%9F-300x-225x12mm.htm</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>11.89</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -4933,7 +4929,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="3" t="n">
-        <v>11.89</v>
+        <v>7.39</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
@@ -4942,7 +4938,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>95 mm high; material PET (not PP)</t>
+          <t>300x225x12 mm vs 300x200x10</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -4953,35 +4949,35 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Hendi Pizzateigbox 600x400, AmerBox, Kitchen Line, 18L, 600x400x(H)95mm</t>
+          <t>Schneidbrett Polyethylen weiß 300 x 200 mm H 15 mm</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-pizzateig-box-kitchen-line-18-l-600-x-400-x-h-95-mm</t>
+          <t>https://www.intergastro.de/schneidbrett-polyethylen-weiss-300-mm-x-200-mm-h-15-mm-158986</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>21.38</v>
+        <v>8.74</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -4993,7 +4989,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="3" t="n">
-        <v>21.38</v>
+        <v>8.74</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -5002,7 +4998,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>95 mm instead of 100 mm; material not stated</t>
+          <t>15 mm thick instead of 10 mm</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5013,39 +5009,39 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble Stapelbarer Pizzateigbehälter 9,5cm (60x40)</t>
+          <t>Hygiplas HDPE kleines Schneidebrett weiß 300x225x12mm</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble</t>
+          <t>Hygiplas</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/x1090@GN-GN537/Gastronoble-Stapelbarer-Pizzateigbeh%C3%A4lter-9-5cm.htm</t>
+          <t>https://www.nisbets.de/hygiplas-hdpe-kleines-schneidebrett-wei-300x-225x12mm/hc867</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>31.9</v>
+        <v>4.89</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
@@ -5053,7 +5049,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="3" t="n">
-        <v>26.81</v>
+        <v>4.89</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -5062,7 +5058,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>95 mm high and polyethylene (vs 100 mm PP)</t>
+          <t>300x225x12 mm vs 300x200x10; other colours 4.89-6.09</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5082,26 +5078,26 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>ALLPAX</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Pizzaballenbehälter, Polyethylen 600x400x100 mm</t>
+          <t>AmerBox Pizzaballenbox 60 x 40 x 9,5 cm</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Stalgast</t>
+          <t>AmerBox</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/pizzaballenbehaelter-polyethylen-600x400x100-mm-bxtxh-1027185</t>
+          <t>https://www.allpax.de/product_info.php/info/AmerBox-Pizzaballenbox-60-x-40-x-9-5-cm.html</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>21.18</v>
+        <v>13.95</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -5113,7 +5109,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="3" t="n">
-        <v>21.18</v>
+        <v>13.95</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
@@ -5122,7 +5118,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Polyethylene instead of PP</t>
+          <t>95 mm high and polyethylene (vs 100 mm PP), 18 l</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5142,26 +5138,26 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Teigwanne - weiß - rechteckig - 60,0 x 40,0 x 9,5 cm - Inhalt 18 l - Polyethylen</t>
+          <t>9-tlg Teigbehälter-Set - 8 Behälter &amp; 1 Deckel - EN 600x400 - Höhe: 100mm - Polypropylen</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/teigwanne-weiss-rechteckig-60-0-x-40-0-x-9-5-cm-inhalt-18-l-polyethylen/202172-C</t>
+          <t>https://www.ggmgastro.com/de-de-eur/9-tlg-teigbehaelter-set-8-behaelter-und-1-deckel-en-600x400-hoehe-100mm-polypropylen-weiss-tbpp6410</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>11</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -5169,11 +5165,15 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>8 boxes + 1 lid</t>
+        </is>
+      </c>
       <c r="K72" s="3" t="n">
-        <v>11</v>
+        <v>9.25</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>95 mm high and polyethylene (vs 100 mm PP); regular price 17.10</t>
+          <t>Only sold as a set of 8 boxes plus 1 lid; net per box includes a share of the lid</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5193,11 +5193,11 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5207,21 +5207,21 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>APS Deckel zu Pizzaballenbehälter</t>
+          <t>Pizzateigbox 18 l 600x400x95 mm</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/aps-deckel-zu-pizzaballenbehaelter-aps82441</t>
+          <t>https://www.gastro-hero.de/products/pizzateigbox-18-l-600x400x95-mm</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>8.69</v>
+        <v>11.89</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -5233,16 +5233,16 @@
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="3" t="n">
-        <v>8.69</v>
+        <v>11.89</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>PE, 600x400x10 mm; min. qty 2</t>
+          <t>95 mm high; material PET (not PP)</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5253,11 +5253,11 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5267,21 +5267,21 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Contacto Deckel zu Pizzaballenbehälter 600 x 400 mm</t>
+          <t>Hendi Pizzateigbox 600x400, AmerBox, Kitchen Line, 18L, 600x400x(H)95mm</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-deckel-zu-pizzaballenbehaelter-fuer-2510</t>
+          <t>https://www.gastrodax.de/hendi-pizzateig-box-kitchen-line-18-l-600-x-400-x-h-95-mm</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>8</v>
+        <v>21.38</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -5293,16 +5293,16 @@
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="3" t="n">
-        <v>8</v>
+        <v>21.38</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>HD-polyethylene; sale price, normal 10.00</t>
+          <t>95 mm instead of 100 mm; material not stated</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5313,11 +5313,11 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble Deckel für stapelbare Pizzateigbehälter 60x40cm</t>
+          <t>Gastronoble Stapelbarer Pizzateigbehälter 9,5cm (60x40)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -5337,11 +5337,11 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/x1090@GN-GN539/Gastronoble-Deckel-f%C3%BCr-stapelbare-Pizzateigbeh%C3%A4lter-60x40cm.htm</t>
+          <t>https://www.gastroladen.de/x1090@GN-GN537/Gastronoble-Stapelbarer-Pizzateigbeh%C3%A4lter-9-5cm.htm</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>27.19</v>
+        <v>31.9</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -5353,16 +5353,16 @@
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="3" t="n">
-        <v>22.85</v>
+        <v>26.81</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>PE lid</t>
+          <t>95 mm high and polyethylene (vs 100 mm PP)</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5373,11 +5373,11 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5387,21 +5387,21 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Deckel für Pizzaballenbehälter, PP, 60 x 40 x 2 cm</t>
+          <t>Pizzaballenbehälter, Polyethylen 600x400x100 mm</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Stalgast</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/deckel-fuer-pizzaballenbehaelter-art-967927-pp-60-x-40-x-2-cm-967928</t>
+          <t>https://www.intergastro.de/pizzaballenbehaelter-polyethylen-600x400x100-mm-bxtxh-1027185</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>7.95</v>
+        <v>21.18</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -5413,14 +5413,18 @@
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="3" t="n">
-        <v>7.95</v>
+        <v>21.18</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Polyethylene instead of PP</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -5429,35 +5433,35 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Deckel - für Teigwanne (202180) - weiß - 60,0 x 40,0 x 3,5 cm - Polypropylen</t>
+          <t>Stapelbarer Pizzateigbehälter 9,5cm (60x40)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Gastronoble</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/deckel-fuer-teigwanne-202180-weiss-rechteckig-60-0-x-40-0-x-3-5-cm-polypropylen/202181-C</t>
+          <t>https://www.nisbets.de/stapelbarer-pizzateigbehlter-95mm/gn537</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>16</v>
+        <v>25.99</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -5469,16 +5473,16 @@
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="3" t="n">
-        <v>16</v>
+        <v>25.99</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>PP lid 600x400; regular price 25.10</t>
+          <t>95 mm high and polyethylene (vs 100 mm PP)</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -5489,35 +5493,35 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>AmerBox Pizzaballenbox 60 x 40 x 7,5 cm</t>
+          <t>APS Deckel zu Pizzaballenbehälter</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>AmerBox</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.de/product_info.php/info/AmerBox-Pizzaballenbox-60-x-40-x-7-5-cm.html</t>
+          <t>https://www.gastro-hero.de/products/aps-deckel-zu-pizzaballenbehaelter-aps82441</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>12.8</v>
+        <v>8.69</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -5529,7 +5533,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="3" t="n">
-        <v>12.8</v>
+        <v>8.69</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5542,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Polyethylene, 14 l</t>
+          <t>PE, 600x400x10 mm; min. qty 2</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -5549,35 +5553,35 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>(8 Stück) Teigbehälter - EN 600x400 - Weiß (70 mm)</t>
+          <t>Contacto Deckel zu Pizzaballenbehälter 600 x 400 mm</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/8-stueck-teigbehaelter-en-600x400-weiss-tbp647</t>
+          <t>https://www.gastrodax.de/contacto-deckel-zu-pizzaballenbehaelter-fuer-2510</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>74.98999999999999</v>
+        <v>8</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -5585,24 +5589,20 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>set of 8</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>9.369999999999999</v>
-      </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>70 mm high, polypropylene (vs 75 mm PE)</t>
+          <t>HD-polyethylene; sale price, normal 10.00</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -5613,39 +5613,39 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Pizzaballenbehälter, weiß Polyethylen, 60x40x7,5cm</t>
+          <t>Gastronoble Deckel für stapelbare Pizzateigbehälter 60x40cm</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Gastronoble</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/pizzaballenbehaelter-weiss-polyethylen-60x40x75cm-2510600</t>
+          <t>https://www.gastroladen.de/x1090@GN-GN539/Gastronoble-Deckel-f%C3%BCr-stapelbare-Pizzateigbeh%C3%A4lter-60x40cm.htm</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>9.99</v>
+        <v>27.19</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
@@ -5653,14 +5653,18 @@
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="3" t="n">
-        <v>9.99</v>
+        <v>22.85</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>PE lid</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -5669,35 +5673,35 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Contacto Pizzaballenbehälter 60 cm / 40 cm (600x400x75 mm)</t>
+          <t>Deckel für Pizzaballenbehälter, PP, 60 x 40 x 2 cm</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-pizzaballenbehaelter-60-cm-40-cm</t>
+          <t>https://www.intergastro.de/deckel-fuer-pizzaballenbehaelter-art-967927-pp-60-x-40-x-2-cm-967928</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -5709,18 +5713,14 @@
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>Polypropylene instead of PE; sale price, normal 12.35. Hendi 600x400x75 (material not stated) 19.43</t>
-        </is>
-      </c>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -5729,21 +5729,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble Stapelbarer Pizzateigbehälter 7,5cm (60x40)</t>
+          <t>Deckel für stapelbare Pizzateigbehälter 60x40cm</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5753,15 +5753,15 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/x1090@GN-GN536/Gastronoble-Stapelbarer-Pizzateigbeh%C3%A4lter-7-5cm.htm</t>
+          <t>https://www.nisbets.de/deckel-fr-stapelbare-pizzateigbehlter-60x40cm/gn539</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>31.9</v>
+        <v>16.99</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="3" t="n">
-        <v>26.81</v>
+        <v>16.99</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -5798,26 +5798,26 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>ALLPAX</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Teigbehälter / Pizzaballenbehälter 14 ltr 600 x 400 mm H 75 mm (Polyethylen)</t>
+          <t>AmerBox Pizzaballenbox 60 x 40 x 7,5 cm</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>AmerBox</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/teigbehaelter-pizzaballenbehaelter-14-ltr-600-mm-x-400-mm-h-75-mm-985534</t>
+          <t>https://www.allpax.de/product_info.php/info/AmerBox-Pizzaballenbox-60-x-40-x-7-5-cm.html</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5829,14 +5829,18 @@
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Polyethylene, 14 l</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -5854,26 +5858,26 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Teig- und Pizzaballenbehälter - weiß - 60,0 x 40,0 x 7,5 cm - Inhalt 14 l - Polyethylen</t>
+          <t>(8 Stück) Teigbehälter - EN 600x400 - Weiß (70 mm)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/teig-und-pizzaballenbehaelter-weiss-60-0-x-40-0-x-7-5-cm-inhalt-14-l-polyethylen/82440-B</t>
+          <t>https://www.ggmgastro.com/de-de-eur/8-stueck-teigbehaelter-en-600x400-weiss-tbp647</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -5881,20 +5885,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>set of 8</t>
+        </is>
+      </c>
       <c r="K84" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Regular price 12.00; Schneider 202170-C same spec 9.50</t>
+          <t>70 mm high, polypropylene (vs 75 mm PE)</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -5905,35 +5913,35 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Hendi Thermobox für GN 1/1</t>
+          <t>Pizzaballenbehälter, weiß Polyethylen, 60x40x7,5cm</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.de/product_info.php/info/Hendi-Thermobox-fuer-GN-1-1.html</t>
+          <t>https://www.gastro-hero.de/products/pizzaballenbehaelter-weiss-polyethylen-60x40x75cm-2510600</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>284</v>
+        <v>9.99</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -5945,18 +5953,14 @@
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="3" t="n">
-        <v>284</v>
+        <v>9.99</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>Front-loading LDPE box with rails, 477x680x620 mm; inner 335x533x590 mm (~105 l, above 80-90 l)</t>
-        </is>
-      </c>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -5965,35 +5969,35 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Porter - Frontlader - 83 Liter - für 12x GN 1/1</t>
+          <t>Contacto Pizzaballenbehälter 60 cm / 40 cm (600x400x75 mm)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/porter-frontlader-83-liter-fuer-12x-gn-1-1-plb-300</t>
+          <t>https://www.gastrodax.de/contacto-pizzaballenbehaelter-60-cm-40-cm</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>274.99</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -6005,16 +6009,16 @@
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="3" t="n">
-        <v>274.99</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>PP, 83 l. Cheaper PU 'Thermobox Frontlader 92 l' (tpbe92): 115.99 net</t>
+          <t>Polypropylene instead of PE; sale price, normal 12.35. Hendi 600x400x75 (material not stated) 19.43</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6025,39 +6029,39 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Thermobox ECO GN 1/1 - Frontlader (90 l)</t>
+          <t>Gastronoble Stapelbarer Pizzateigbehälter 7,5cm (60x40)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Gastronoble</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/thermobox-eco-gn-1-1-frontlader-thbe90</t>
+          <t>https://www.gastroladen.de/x1090@GN-GN536/Gastronoble-Stapelbarer-Pizzateigbeh%C3%A4lter-7-5cm.htm</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>169.9</v>
+        <v>31.9</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
@@ -6065,7 +6069,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="3" t="n">
-        <v>169.9</v>
+        <v>26.81</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -6074,7 +6078,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>90 l; sale price (normal 349.00 net)</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6085,35 +6089,35 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Contacto Thermobox GN 1/1 Frontlader, 12 Auflageschienen</t>
+          <t>Teigbehälter / Pizzaballenbehälter 14 ltr 600 x 400 mm H 75 mm (Polyethylen)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-thermobox-gn-1-1-1</t>
+          <t>https://www.intergastro.de/teigbehaelter-pizzaballenbehaelter-14-ltr-600-mm-x-400-mm-h-75-mm-985534</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>229.14</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -6125,18 +6129,14 @@
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="3" t="n">
-        <v>229.14</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>Front loader GN 1/1, 495x635x630 mm outside; volume not stated; sale price, normal 342.00</t>
-        </is>
-      </c>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -6145,39 +6145,39 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Cambro isolierter Frontlader Lebensmitteltransportbehälter 86L</t>
+          <t>Stapelbehälter 60x40x7,5cm</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Cambro</t>
+          <t>Gastronoble</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/0860@GN-DW565/Cambro-isolierter-Frontlader-Lebensmitteltransportbeh%C3%A4lter-86L.htm</t>
+          <t>https://www.nisbets.de/stapelbarer-pizzateigbehlter-75mm/gn536</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>324.9</v>
+        <v>25.99</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="3" t="n">
-        <v>273.03</v>
+        <v>25.99</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>For 4 x GN 1/1 100 mm; bulky item</t>
+          <t>Polyethylene</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6214,26 +6214,26 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>ALLPAX</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Box COMBI schwarz, 12 Einschübe, 83 ltr, 630 x 500 x 580 mm</t>
+          <t>Hendi Thermobox für GN 1/1</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Thermohauser</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/box-combi-schwarz-12-einschuebe-83-ltr-630-mm-x-500-mm-h-580-mm-305715</t>
+          <t>https://www.allpax.de/product_info.php/info/Hendi-Thermobox-fuer-GN-1-1.html</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>265.95</v>
+        <v>284</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -6245,16 +6245,16 @@
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="3" t="n">
-        <v>265.95</v>
+        <v>284</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Front-loader category; also Schneider Front-Box GN 1/1 91 l at 218.07 net</t>
+          <t>Front-loading LDPE box with rails, 477x680x620 mm; inner 335x533x590 mm (~105 l, above 80-90 l)</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -6274,26 +6274,26 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>FRONT-BOX - 62,8 x 44,5 x 62,5 cm - Inhalt 91 l - GN 1/1 - EPP</t>
+          <t>Porter - Frontlader - 83 Liter - für 12x GN 1/1</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/front-box-62-8-x-44-5-x-62-5-cm-inhalt-91-l-gn-1-1-epp/620660-C</t>
+          <t>https://www.ggmgastro.com/de-de-eur/porter-frontlader-83-liter-fuer-12x-gn-1-1-plb-300</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>196</v>
+        <v>274.99</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -6305,16 +6305,16 @@
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="3" t="n">
-        <v>196</v>
+        <v>274.99</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>91 l (slightly above 80-90 l), EPP front loader; regular price 318.75</t>
+          <t>PP, 83 l. Cheaper PU 'Thermobox Frontlader 92 l' (tpbe92): 115.99 net</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -6325,31 +6325,35 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>EN Tablett, Serie Tray 97, 53x37 cm</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
+          <t>Thermobox ECO GN 1/1 - Frontlader (90 l)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.de/product_info.php/info/EN-Tablett.html</t>
+          <t>https://www.gastro-hero.de/products/thermobox-eco-gn-1-1-frontlader-thbe90</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>19.22</v>
+        <v>169.9</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -6361,16 +6365,16 @@
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="3" t="n">
-        <v>19.22</v>
+        <v>169.9</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Right size but fibreglass-reinforced polyester, not ABS/PP</t>
+          <t>90 l; sale price (normal 349.00 net)</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -6381,35 +6385,35 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>(6 Stück) FAST FOOD Tablett - GN 1/1 - Polypropylen - Höhe 20mm - Schwarz</t>
+          <t>Contacto Thermobox GN 1/1 Frontlader, 12 Auflageschienen</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>GGM</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-de-eur/6-stueck-fast-food-tablett-gn-1-1-polypropylen-hoehe-20mm-schwarz-00553-6</t>
+          <t>https://www.gastrodax.de/contacto-thermobox-gn-1-1-1</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>34.99</v>
+        <v>229.14</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -6417,24 +6421,20 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>set of 6</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="3" t="n">
-        <v>5.83</v>
+        <v>229.14</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>PP but GN 1/1 size (530x325), not 530x370</t>
+          <t>Front loader GN 1/1, 495x635x630 mm outside; volume not stated; sale price, normal 342.00</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -6445,39 +6445,39 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany Tablett PP - GN 1/1, lichtgrau</t>
+          <t>Cambro isolierter Frontlader Lebensmitteltransportbehälter 86L</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Cambro</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/was-germany-tablett-pp-gn-11-lichtgrau-9283530</t>
+          <t>https://www.gastroladen.de/0860@GN-DW565/Cambro-isolierter-Frontlader-Lebensmitteltransportbeh%C3%A4lter-86L.htm</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>6.59</v>
+        <v>324.9</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
@@ -6485,16 +6485,16 @@
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="3" t="n">
-        <v>6.59</v>
+        <v>273.03</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>PP but GN 1/1 size (530x325), not 370x530</t>
+          <t>For 4 x GN 1/1 100 mm; bulky item</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -6505,35 +6505,35 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Hendi Serviertablett, rechteckig, Euronorm, 370x530mm</t>
+          <t>Box COMBI schwarz, 12 Einschübe, 83 ltr, 630 x 500 x 580 mm</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Thermohauser</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-serviertablett-rechteckig-euronorm-370-x-530-mm</t>
+          <t>https://www.intergastro.de/box-combi-schwarz-12-einschuebe-83-ltr-630-mm-x-500-mm-h-580-mm-305715</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>15.25</v>
+        <v>265.95</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -6545,16 +6545,16 @@
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="3" t="n">
-        <v>15.25</v>
+        <v>265.95</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Exact size; material not stated on page</t>
+          <t>Front-loader category; also Schneider Front-Box GN 1/1 91 l at 218.07 net</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -6565,39 +6565,39 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Kristallon Serviertablett antirutsch 51 x 38cm</t>
+          <t>Cambro isolierter Frontlader Lebensmitteltransportbehälter 86Ltr</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Kristallon</t>
+          <t>Cambro</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/G16801@GN-C560/Kristallon-Serviertablett-antirutsch-51-x-38cm.htm</t>
+          <t>https://www.nisbets.de/cambro-isolierter-frontlader-lebensmitteltransportbehaelter-86ltr/dw565</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>239.99</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
@@ -6605,16 +6605,16 @@
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="3" t="n">
-        <v>7.47</v>
+        <v>239.99</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>510x380 mm, plastic (type not specified), non-slip</t>
+          <t>For 4 x GN 1/1 100 mm, PP; out of stock; UVP 264.99. Thermo Future 93 l front-loader (DL990) 209.99</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -6634,26 +6634,22 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>ALLPAX</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Tablett Polyester titanfarben rechteckig 530 x 370 mm</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Cambro</t>
-        </is>
-      </c>
+          <t>EN Tablett, Serie Tray 97, 53x37 cm</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/tablett-polyester-titanfarben-rechteckig-530-mm-x-370-mm-396106</t>
+          <t>https://www.allpax.de/product_info.php/info/EN-Tablett.html</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>18.19</v>
+        <v>19.22</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -6665,7 +6661,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="3" t="n">
-        <v>18.19</v>
+        <v>19.22</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -6674,7 +6670,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>Right size but polyester/fibreglass, not ABS/PP; no ABS/PP tray of this size found</t>
+          <t>Right size but fibreglass-reinforced polyester, not ABS/PP</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -6694,26 +6690,26 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com [substitute]</t>
+          <t>GGM Gastro</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Euronorm-Tablett - Stapelnocken - Serie 9605 - lichtgrau - 53 x 37 cm - Polyester</t>
+          <t>(6 Stück) FAST FOOD Tablett - GN 1/1 - Polypropylen - Höhe 20mm - Schwarz</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/euronorm-tablett-stapelnocken-serie-9605-lichtgrau-53-x-37-cm-polyester/9605531-A</t>
+          <t>https://www.ggmgastro.com/de-de-eur/6-stueck-fast-food-tablett-gn-1-1-polypropylen-hoehe-20mm-schwarz-00553-6</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>11.9</v>
+        <v>34.99</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -6721,11 +6717,15 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
       <c r="K98" s="3" t="n">
-        <v>11.9</v>
+        <v>5.83</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Right size but polyester (not ABS/PP); PP non-slip tray 46x36 cm 6.10; regular price 17.50</t>
+          <t>PP but GN 1/1 size (530x325), not 530x370</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -6745,35 +6745,35 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX</t>
+          <t>GastroHero</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Thermo-Tablett rechteckig 5-teilig 430x290x(H)150 mm</t>
+          <t>WAS Germany Tablett PP - GN 1/1, lichtgrau</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.de/product_info.php/info/Thermo-Tablett-rechteckig.html</t>
+          <t>https://www.gastro-hero.de/products/was-germany-tablett-pp-gn-11-lichtgrau-9283530</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>36.09</v>
+        <v>6.59</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -6785,16 +6785,16 @@
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="3" t="n">
-        <v>36.09</v>
+        <v>6.59</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>5-piece set (ABS base, stainless tray, transparent hood, 2 cooling packs); 5 parts rather than 5 compartments</t>
+          <t>PP but GN 1/1 size (530x325), not 370x530</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -6805,35 +6805,35 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Gastrodax [substitute]</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>APS Thermo-Set 5-tlg. ca. Ø 38 cm, Höhe 24 cm</t>
+          <t>Hendi Serviertablett, rechteckig, Euronorm, 370x530mm</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.de/products/aps-thermo-set-5-tlg-ca-38-cm-hoehe-24-cm-aps09082</t>
+          <t>https://www.gastrodax.de/hendi-serviertablett-rechteckig-euronorm-370-x-530-mm</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>44.9</v>
+        <v>15.25</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -6845,16 +6845,16 @@
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="3" t="n">
-        <v>44.9</v>
+        <v>15.25</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Round 5-piece set (stainless bowl, tray, roll-top hood, 2 cooling packs); not a compartment tray; min. qty 2</t>
+          <t>Exact size; material not stated on page</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -6865,39 +6865,39 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute]</t>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>APS Thermo Tablett Set rechteckig (5-teilig)</t>
+          <t>Kristallon Serviertablett antirutsch 51 x 38cm</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Kristallon</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/aps-thermo-tablett-set-rechteckig</t>
+          <t>https://www.gastroladen.de/G16801@GN-C560/Kristallon-Serviertablett-antirutsch-51-x-38cm.htm</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>26.19</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="3" t="n">
-        <v>26.19</v>
+        <v>7.47</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>5-piece set: insulated plastic base, stainless tray, PS lid, 2 cooling packs; 430x290x140 mm; 5 parts rather than 5 compartments</t>
+          <t>510x380 mm, plastic (type not specified), non-slip</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -6925,21 +6925,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Intergastro</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Cambro Tablotherm Isolierte Schale mit Porzellantellern 37 x 53 x 10,5 cm</t>
+          <t>Tablett Polyester titanfarben rechteckig 530 x 370 mm</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6949,15 +6949,15 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.de/0860@GN-CJ645/Cambro-Tablotherm-Isolierte-Schale-mit-Porzellantellern-37-x-53-x-10-5-cm.htm</t>
+          <t>https://www.intergastro.de/tablett-polyester-titanfarben-rechteckig-530-mm-x-370-mm-396106</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>254.9</v>
+        <v>18.19</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="3" t="n">
-        <v>214.2</v>
+        <v>18.19</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>Insulated tray with porcelain 2-compartment plate + 3 bowls with lids; not a simple 5-6 compartment thermo tray</t>
+          <t>Right size but polyester/fibreglass, not ABS/PP; no ABS/PP tray of this size found</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -6985,35 +6985,35 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Intergastro</t>
+          <t>Nisbets</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Tablett TABLOTHERM EURONORM isoliert mit Geschirr, Deckel, Pellet</t>
+          <t>Olympia Kristallon Serviertablett antirutsch 51 x 38cm</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Cambro</t>
+          <t>Olympia Kristallon</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.de/tablett-tablotherm-euronorm-isoliert-mit-geschirr-deckel-pellet-325159</t>
+          <t>https://www.nisbets.de/kristallon-anti-rutsch-serviertablett-rechteckig-51cm/c560</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>176.33</v>
+        <v>5.09</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -7025,19 +7025,379 @@
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="3" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>510x380 mm, plastic (type not specified), non-slip; 4.49 each from 3 pcs</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Thermo-Tablett rechteckig 5-teilig 430x290x(H)150 mm</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.de/product_info.php/info/Thermo-Tablett-rechteckig.html</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="3" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>5-piece set (ABS base, stainless tray, transparent hood, 2 cooling packs); 5 parts rather than 5 compartments</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>APS Thermo-Set 5-tlg. ca. Ø 38 cm, Höhe 24 cm</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.de/products/aps-thermo-set-5-tlg-ca-38-cm-hoehe-24-cm-aps09082</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Round 5-piece set (stainless bowl, tray, roll-top hood, 2 cooling packs); not a compartment tray; min. qty 2</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax [substitute]</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>APS Thermo Tablett Set rechteckig (5-teilig)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/aps-thermo-tablett-set-rechteckig</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="3" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>5-piece set: insulated plastic base, stainless tray, PS lid, 2 cooling packs; 430x290x140 mm; 5 parts rather than 5 compartments</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.de (Harotec GmbH) [substitute]</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Cambro Tablotherm Isolierte Schale mit Porzellantellern 37 x 53 x 10,5 cm</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.de/0860@GN-CJ645/Cambro-Tablotherm-Isolierte-Schale-mit-Porzellantellern-37-x-53-x-10-5-cm.htm</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="3" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>Insulated tray with porcelain 2-compartment plate + 3 bowls with lids; not a simple 5-6 compartment thermo tray</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Tablett TABLOTHERM EURONORM isoliert mit Geschirr, Deckel, Pellet</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.de/tablett-tablotherm-euronorm-isoliert-mit-geschirr-deckel-pellet-325159</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
         <v>176.33</v>
       </c>
-      <c r="L103" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="3" t="n">
+        <v>176.33</v>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
         <is>
           <t>APPROX</t>
         </is>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Insulated PP tray system incl. dishes, lid and heat pellet; not a simple 5-6 compartment thermo tray</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Nisbets</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Cambro Tablotherm Isolierte Schale mit Porzellantellern 37 x 53 x 10,5 cm</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nisbets.de/cambro-tablotherm-isolierte-schale-mit-porzellantellern-37-x-53-x-105-cm/cj645</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>177.99</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="3" t="n">
+        <v>177.99</v>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>Insulated tray with 2-compartment porcelain plate + 3 bowls with lids; not a simple 5-6 compartment thermo tray; 2-3 weeks delivery</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
@@ -7122,17 +7482,17 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>7.5</v>
+        <v>7.26</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>13.98</v>
+        <v>12.24</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>22.43</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -7152,17 +7512,17 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7.29</v>
+        <v>5.82</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>18.75</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>ALLPAX, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -7192,7 +7552,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -7222,7 +7582,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -7239,20 +7599,20 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1.42</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro</t>
+          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -7269,20 +7629,20 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.76</v>
+        <v>2.35</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>5.33</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro</t>
+          <t>GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -7306,7 +7666,7 @@
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -7325,14 +7685,14 @@
         <v>18.09</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>30.17</v>
+        <v>27.49</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>93.66</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -7355,14 +7715,14 @@
         <v>17.29</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>22.09</v>
+        <v>23.49</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>26.95</v>
+        <v>31.04</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -7379,20 +7739,20 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>28.49</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>34.27</v>
+        <v>35.05</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>49.39</v>
+        <v>57.99</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro</t>
+          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -7409,20 +7769,20 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>7.39</v>
+        <v>4.89</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>8.74</v>
+        <v>8.06</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>15.76</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro</t>
+          <t>Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -7445,14 +7805,14 @@
         <v>9.25</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>13.95</v>
+        <v>21.18</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>26.81</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -7482,7 +7842,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -7502,17 +7862,17 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>26.81</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -7542,7 +7902,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, shopbuero.com [substitute]</t>
+          <t>ALLPAX, GGM Gastro, GastroHero, Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Intergastro, Nisbets</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -7559,24 +7919,24 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>7.47</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>11.36</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>15.25</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute]</t>
+          <t>Gastrodax [substitute], Gastroladen.de (Harotec GmbH) [substitute], Nisbets</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -7606,7 +7966,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -7644,7 +8004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7699,7 +8059,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Blocks automated access: all lusini.com pages (incl. robots.txt) return HTTP 403 to scripts and to the web-fetch tool; no price could be read or verified. Checked 2026-09-30.</t>
+          <t>Blocks automated access: all lusini.com pages (incl. robots.txt) return HTTP 403 to scripts and to the web-fetch tool; no price could be read or verified. Checked 2026-09-30. Re-tested with a headless Chromium browser: the Cloudflare 'Sicherheitsüberprüfung wird durchgeführt' (bot check) page never clears, even after 25 s, so the shop cannot be read without bot-detection evasion (not attempted).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7711,52 +8071,25 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Nisbets Germany</t>
+          <t>METRO Germany</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.nisbets.de</t>
+          <t>https://www.metro.de/marktplatz</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>pan-EU</t>
+          <t>marketplace</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Blocks automated access: every nisbets.de URL (incl. robots.txt/sitemap) returns HTTP 403 with a Cloudflare 'Just a moment...' bot challenge; the web-fetch tool is also refused. No price readable.</t>
+          <t>Blocks automated access: www.metro.de including the METRO Marktplatz returns HTTP 403 to scripts and to the web-fetch tool; produkte.metro.de is a JavaScript-only page with no readable product data; shop.metro.de (customer shop) returned 503 / needs a customer login. Re-tested with a headless Chromium browser: METRO returns an access-denied page ('ARE YOU LOST? Sorry, only our team of experts has access here.') for both the Marktplatz start page and product pages.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Much of the Nisbets range (Vogue, Hygiplas, Cambro, Gastronoble) is priced at Gastroladen.de (substitute).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>METRO Germany</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.metro.de/marktplatz</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>marketplace</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Blocks automated access: www.metro.de including the METRO Marktplatz returns HTTP 403 to scripts and to the web-fetch tool; produkte.metro.de is a JavaScript-only page with no readable product data; shop.metro.de (customer shop) returned 503 / needs a customer login.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Search-engine snippets show METRO Professional PC GN containers on the METRO Marktplatz (e.g. GN 1/1 100 mm, GN 1/2 150 mm), but the prices could not be confirmed on the site, so none were recorded.</t>
         </is>
